--- a/_work/analysis/02_сравнение_залог.xlsx
+++ b/_work/analysis/02_сравнение_залог.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Остатки чужих данных" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Статус и полнота чтения" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Проверка цитат" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Поправки (этап 3)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -70,6 +76,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15684,4 +15691,119 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>При подготовке этапа 3 найдены неточности этапа 2. Лист «Сравнение» не переписан: читайте его вместе с этим листом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Строка</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Было в таблице этапа 2</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Исправление (по исходному тексту)</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Как проверено</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ответственность</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>в №17 ВКО ГЧП перехода прав и обязанностей к наследникам нет</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>есть (раздел «Ответственность»: «…обязательства и права по настоящему Договору переходят к его наследнику (наследникам)…»); по тексту положения о наследниках нет в №1, №7, №16, №29, №33, №34</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>grep «наследник» по _work/text/, этап 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Реквизиты/подписи</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>банки из банковских реквизитов (АО «Fortebank», АО «Банк ЦентрКредит», АО «Народный Банк Казахстана», АО «BEREKE BANK») указаны как Поверенный/Заемщик/Партнер; Комитет Казначейства МФ РК и КГД МФ РК — как залогодержатели</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>это банки и органы из платежных реквизитов, а не стороны договора; состав сторон — по преамбуле (см. 03_унификация.md, раздел 2.1)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>сверка агентом этапа 3 с текстом, выборочно подтверждено</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Порядок обращения взыскания и реализации (судебный/внесудебный)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>№17, №18 ВКО — только судебная реализация</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>только в русском тексте (п. 2.3, 2.5); в казахском тексте — «сот және соттан тыс» (судебная и внесудебная)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>grep по _work/text/, этап 3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/_work/analysis/02_сравнение_залог.xlsx
+++ b/_work/analysis/02_сравнение_залог.xlsx
@@ -15699,7 +15699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15803,6 +15803,28 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ответственность</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>получатель штрафов 10%/5% в №50, №24 Прил.3 и Прил.3-1 не указан</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>получатель — Залогодержатель: №50 разд. 5; №24 Прил.3 (текст, стр. 1869); №24 Прил.3-1 п. 5.4 (текст, стр. 2301, плательщик — Заемщик)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>grep по _work/text/, этап 4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
